--- a/artfynd/A 42342-2022 artfynd.xlsx
+++ b/artfynd/A 42342-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42342-2022 artfynd.xlsx
+++ b/artfynd/A 42342-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104797097</v>
+        <v>104797077</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
+        <v>78569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447211.012121458</v>
+        <v>447655.0279278303</v>
       </c>
       <c r="R4" t="n">
-        <v>6918515.829831171</v>
+        <v>6918157.249614066</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105226538</v>
+        <v>104797087</v>
       </c>
       <c r="B5" t="n">
-        <v>76486</v>
+        <v>78569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,35 +1030,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447486.9687527321</v>
+        <v>447471.1999542807</v>
       </c>
       <c r="R5" t="n">
-        <v>6918489.218997714</v>
+        <v>6918254.298169499</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105226503</v>
+        <v>104797047</v>
       </c>
       <c r="B6" t="n">
-        <v>79433</v>
+        <v>78569</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1143,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447486.9687527321</v>
+        <v>447634.8820382358</v>
       </c>
       <c r="R6" t="n">
-        <v>6918489.218997714</v>
+        <v>6918087.055824849</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110975795</v>
+        <v>104797069</v>
       </c>
       <c r="B7" t="n">
-        <v>76918</v>
+        <v>78569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,40 +1256,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447263.7685503919</v>
+        <v>447573.4690648131</v>
       </c>
       <c r="R7" t="n">
-        <v>6918503.401348694</v>
+        <v>6918140.436708981</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,22 +1311,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,29 +1335,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110975584</v>
+        <v>104797057</v>
       </c>
       <c r="B8" t="n">
-        <v>76495</v>
+        <v>89673</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,40 +1369,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447506.0012030424</v>
+        <v>447587.3583995553</v>
       </c>
       <c r="R8" t="n">
-        <v>6918488.456190935</v>
+        <v>6918137.435649394</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,22 +1424,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,29 +1448,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110976097</v>
+        <v>104797097</v>
       </c>
       <c r="B9" t="n">
-        <v>78081</v>
+        <v>77258</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,40 +1482,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447184.2951792</v>
+        <v>447211.012121458</v>
       </c>
       <c r="R9" t="n">
-        <v>6918559.387356906</v>
+        <v>6918515.829831171</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,22 +1537,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,29 +1561,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110962616</v>
+        <v>104797050</v>
       </c>
       <c r="B10" t="n">
-        <v>78081</v>
+        <v>78569</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,35 +1595,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447067.8937680415</v>
+        <v>447669.6716562179</v>
       </c>
       <c r="R10" t="n">
-        <v>6918659.093284038</v>
+        <v>6918113.41606515</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,22 +1650,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,22 +1680,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110966966</v>
+        <v>105226538</v>
       </c>
       <c r="B11" t="n">
-        <v>78107</v>
+        <v>76486</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,38 +1708,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447585.549203762</v>
+        <v>447486.9687527321</v>
       </c>
       <c r="R11" t="n">
-        <v>6918288.683952288</v>
+        <v>6918489.218997714</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,7 +1763,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1782,7 +1773,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1802,22 +1793,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110966278</v>
+        <v>105226503</v>
       </c>
       <c r="B12" t="n">
-        <v>78107</v>
+        <v>79433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,13 +1846,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447497.9045277975</v>
+        <v>447486.9687527321</v>
       </c>
       <c r="R12" t="n">
-        <v>6918505.281104221</v>
+        <v>6918489.218997714</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1876,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1895,7 +1886,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2022-11-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1927,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110965319</v>
+        <v>110975795</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
+        <v>76918</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,42 +1930,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447291.9897770986</v>
+        <v>447263.7685503919</v>
       </c>
       <c r="R13" t="n">
-        <v>6918584.588592289</v>
+        <v>6918503.401348694</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2022,28 +2015,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110966444</v>
+        <v>110975584</v>
       </c>
       <c r="B14" t="n">
-        <v>76918</v>
+        <v>76495</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,38 +2050,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447564.2989728634</v>
+        <v>447506.0012030424</v>
       </c>
       <c r="R14" t="n">
-        <v>6918385.033740349</v>
+        <v>6918488.456190935</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,28 +2131,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110965310</v>
+        <v>110976097</v>
       </c>
       <c r="B15" t="n">
-        <v>78107</v>
+        <v>78081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,38 +2166,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447291.9897770986</v>
+        <v>447184.2951792</v>
       </c>
       <c r="R15" t="n">
-        <v>6918584.588592289</v>
+        <v>6918559.387356906</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2248,28 +2247,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110965155</v>
+        <v>110962616</v>
       </c>
       <c r="B16" t="n">
-        <v>89558</v>
+        <v>78081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,42 +2278,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447265.5391782096</v>
+        <v>447067.8937680415</v>
       </c>
       <c r="R16" t="n">
-        <v>6918615.617490559</v>
+        <v>6918659.093284038</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,22 +2367,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110976192</v>
+        <v>110966966</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
+        <v>78107</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,45 +2391,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447155.653018409</v>
+        <v>447585.549203762</v>
       </c>
       <c r="R17" t="n">
-        <v>6918628.020806503</v>
+        <v>6918288.683952288</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,29 +2474,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110975579</v>
+        <v>110966278</v>
       </c>
       <c r="B18" t="n">
-        <v>89558</v>
+        <v>78107</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,44 +2504,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447357.8804627243</v>
+        <v>447497.9045277975</v>
       </c>
       <c r="R18" t="n">
-        <v>6918521.398350791</v>
+        <v>6918505.281104221</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,29 +2587,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110975716</v>
+        <v>110965319</v>
       </c>
       <c r="B19" t="n">
-        <v>78081</v>
+        <v>96348</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,44 +2617,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447501.6072664696</v>
+        <v>447291.9897770986</v>
       </c>
       <c r="R19" t="n">
-        <v>6918297.422973903</v>
+        <v>6918584.588592289</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2709,29 +2700,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110963767</v>
+        <v>110966444</v>
       </c>
       <c r="B20" t="n">
-        <v>77186</v>
+        <v>76918</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,35 +2734,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447158.8766089129</v>
+        <v>447564.2989728634</v>
       </c>
       <c r="R20" t="n">
-        <v>6918685.017929589</v>
+        <v>6918385.033740349</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2841,10 +2831,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110962666</v>
+        <v>110965310</v>
       </c>
       <c r="B21" t="n">
-        <v>77268</v>
+        <v>78107</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,38 +2847,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447067.8937680415</v>
+        <v>447291.9897770986</v>
       </c>
       <c r="R21" t="n">
-        <v>6918659.093284038</v>
+        <v>6918584.588592289</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2942,22 +2932,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110963196</v>
+        <v>110965155</v>
       </c>
       <c r="B22" t="n">
-        <v>96348</v>
+        <v>89558</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2970,35 +2960,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447157.6888229793</v>
+        <v>447265.5391782096</v>
       </c>
       <c r="R22" t="n">
-        <v>6918698.023132101</v>
+        <v>6918615.617490559</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3055,22 +3045,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110966770</v>
+        <v>110976192</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>96348</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,42 +3069,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447624.7493553119</v>
+        <v>447155.653018409</v>
       </c>
       <c r="R23" t="n">
-        <v>6918329.816104956</v>
+        <v>6918628.020806503</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3162,28 +3155,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110968694</v>
+        <v>110975579</v>
       </c>
       <c r="B24" t="n">
-        <v>77186</v>
+        <v>89558</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3192,42 +3186,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447196.2663418549</v>
+        <v>447357.8804627243</v>
       </c>
       <c r="R24" t="n">
-        <v>6918552.704730005</v>
+        <v>6918521.398350791</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3275,28 +3271,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110969212</v>
+        <v>110975716</v>
       </c>
       <c r="B25" t="n">
-        <v>96348</v>
+        <v>78081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3305,42 +3302,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447122.915725525</v>
+        <v>447501.6072664696</v>
       </c>
       <c r="R25" t="n">
-        <v>6918672.60023027</v>
+        <v>6918297.422973903</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,28 +3387,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110966289</v>
+        <v>110963767</v>
       </c>
       <c r="B26" t="n">
-        <v>78081</v>
+        <v>77186</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3422,35 +3422,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447497.9045277975</v>
+        <v>447158.8766089129</v>
       </c>
       <c r="R26" t="n">
-        <v>6918505.281104221</v>
+        <v>6918685.017929589</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110975458</v>
+        <v>110962666</v>
       </c>
       <c r="B27" t="n">
-        <v>96348</v>
+        <v>77268</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3531,45 +3531,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447213.6780305866</v>
+        <v>447067.8937680415</v>
       </c>
       <c r="R27" t="n">
-        <v>6918684.615708083</v>
+        <v>6918659.093284038</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3617,29 +3614,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110975486</v>
+        <v>110963196</v>
       </c>
       <c r="B28" t="n">
-        <v>78578</v>
+        <v>96348</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3648,44 +3644,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447210.9753919402</v>
+        <v>447157.6888229793</v>
       </c>
       <c r="R28" t="n">
-        <v>6918660.54063332</v>
+        <v>6918698.023132101</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3733,29 +3727,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110966545</v>
+        <v>110966770</v>
       </c>
       <c r="B29" t="n">
-        <v>76495</v>
+        <v>79444</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3768,38 +3761,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447615.3900424382</v>
+        <v>447624.7493553119</v>
       </c>
       <c r="R29" t="n">
-        <v>6918384.696453596</v>
+        <v>6918329.816104956</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3853,22 +3846,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110976451</v>
+        <v>110968694</v>
       </c>
       <c r="B30" t="n">
-        <v>78578</v>
+        <v>77186</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3881,40 +3874,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447063.1056956617</v>
+        <v>447196.2663418549</v>
       </c>
       <c r="R30" t="n">
-        <v>6918738.015169982</v>
+        <v>6918552.704730005</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3962,29 +3953,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110965542</v>
+        <v>110969212</v>
       </c>
       <c r="B31" t="n">
-        <v>78081</v>
+        <v>96348</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3993,42 +3983,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447365.1558644402</v>
+        <v>447122.915725525</v>
       </c>
       <c r="R31" t="n">
-        <v>6918570.448676185</v>
+        <v>6918672.60023027</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4082,22 +4072,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110976079</v>
+        <v>110966289</v>
       </c>
       <c r="B32" t="n">
-        <v>76495</v>
+        <v>78081</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4110,40 +4100,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447259.1540010307</v>
+        <v>447497.9045277975</v>
       </c>
       <c r="R32" t="n">
-        <v>6918505.329467906</v>
+        <v>6918505.281104221</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4191,29 +4179,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110975647</v>
+        <v>110975458</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>96348</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4222,30 +4209,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4253,10 +4241,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447621.9338528389</v>
+        <v>447213.6780305866</v>
       </c>
       <c r="R33" t="n">
-        <v>6918328.00482947</v>
+        <v>6918684.615708083</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,10 +4314,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110975705</v>
+        <v>110975486</v>
       </c>
       <c r="B34" t="n">
-        <v>78081</v>
+        <v>78578</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4342,21 +4330,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4369,10 +4357,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447621.9338528389</v>
+        <v>447210.9753919402</v>
       </c>
       <c r="R34" t="n">
-        <v>6918328.00482947</v>
+        <v>6918660.54063332</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4442,10 +4430,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110975517</v>
+        <v>110966545</v>
       </c>
       <c r="B35" t="n">
-        <v>89558</v>
+        <v>76495</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4454,44 +4442,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447239.1915552524</v>
+        <v>447615.3900424382</v>
       </c>
       <c r="R35" t="n">
-        <v>6918653.137988863</v>
+        <v>6918384.696453596</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4539,29 +4525,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110975558</v>
+        <v>110976451</v>
       </c>
       <c r="B36" t="n">
-        <v>77267</v>
+        <v>78578</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4574,21 +4559,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4601,10 +4586,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447280.384271103</v>
+        <v>447063.1056956617</v>
       </c>
       <c r="R36" t="n">
-        <v>6918614.455664258</v>
+        <v>6918738.015169982</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4674,7 +4659,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>110962674</v>
+        <v>110965542</v>
       </c>
       <c r="B37" t="n">
         <v>78081</v>
@@ -4711,17 +4696,17 @@
       <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447058.9192056892</v>
+        <v>447365.1558644402</v>
       </c>
       <c r="R37" t="n">
-        <v>6918737.617692174</v>
+        <v>6918570.448676185</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4775,22 +4760,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>110964390</v>
+        <v>110976079</v>
       </c>
       <c r="B38" t="n">
-        <v>89419</v>
+        <v>76495</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4803,38 +4788,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447249.0090083955</v>
+        <v>447259.1540010307</v>
       </c>
       <c r="R38" t="n">
-        <v>6918657.157264436</v>
+        <v>6918505.329467906</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4882,28 +4869,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>110966541</v>
+        <v>110975647</v>
       </c>
       <c r="B39" t="n">
-        <v>78081</v>
+        <v>79444</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4916,38 +4904,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447615.3900424382</v>
+        <v>447621.9338528389</v>
       </c>
       <c r="R39" t="n">
-        <v>6918384.696453596</v>
+        <v>6918328.00482947</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4995,25 +4985,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>110965765</v>
+        <v>110975705</v>
       </c>
       <c r="B40" t="n">
         <v>78081</v>
@@ -5047,20 +5038,22 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447398.736648504</v>
+        <v>447621.9338528389</v>
       </c>
       <c r="R40" t="n">
-        <v>6918579.196305797</v>
+        <v>6918328.00482947</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5108,25 +5101,26 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110965631</v>
+        <v>110975517</v>
       </c>
       <c r="B41" t="n">
         <v>89558</v>
@@ -5160,20 +5154,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447402.1524191221</v>
+        <v>447239.1915552524</v>
       </c>
       <c r="R41" t="n">
-        <v>6918560.126074024</v>
+        <v>6918653.137988863</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5221,28 +5217,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110968265</v>
+        <v>110975558</v>
       </c>
       <c r="B42" t="n">
-        <v>76495</v>
+        <v>77267</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5255,38 +5252,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447317.6738993236</v>
+        <v>447280.384271103</v>
       </c>
       <c r="R42" t="n">
-        <v>6918445.963964912</v>
+        <v>6918614.455664258</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5334,28 +5333,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110965265</v>
+        <v>110962674</v>
       </c>
       <c r="B43" t="n">
-        <v>89369</v>
+        <v>78081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5364,25 +5364,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447265.5391782096</v>
+        <v>447058.9192056892</v>
       </c>
       <c r="R43" t="n">
-        <v>6918615.617490559</v>
+        <v>6918737.617692174</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110966438</v>
+        <v>110964390</v>
       </c>
       <c r="B44" t="n">
-        <v>78107</v>
+        <v>89419</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5481,35 +5481,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447564.2989728634</v>
+        <v>447249.0090083955</v>
       </c>
       <c r="R44" t="n">
-        <v>6918385.033740349</v>
+        <v>6918657.157264436</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110975542</v>
+        <v>110966541</v>
       </c>
       <c r="B45" t="n">
-        <v>77267</v>
+        <v>78081</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5594,40 +5594,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447292.5455528187</v>
+        <v>447615.3900424382</v>
       </c>
       <c r="R45" t="n">
-        <v>6918619.829575079</v>
+        <v>6918384.696453596</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5675,29 +5673,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110975964</v>
+        <v>110965765</v>
       </c>
       <c r="B46" t="n">
-        <v>96348</v>
+        <v>78081</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5706,45 +5703,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447263.7685503919</v>
+        <v>447398.736648504</v>
       </c>
       <c r="R46" t="n">
-        <v>6918503.401348694</v>
+        <v>6918579.196305797</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5792,29 +5786,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>110976438</v>
+        <v>110965631</v>
       </c>
       <c r="B47" t="n">
-        <v>96348</v>
+        <v>89558</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5827,41 +5820,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447113.0834828347</v>
+        <v>447402.1524191221</v>
       </c>
       <c r="R47" t="n">
-        <v>6918667.653965114</v>
+        <v>6918560.126074024</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5909,29 +5899,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>110962617</v>
+        <v>110968265</v>
       </c>
       <c r="B48" t="n">
-        <v>77267</v>
+        <v>76495</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5944,38 +5933,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447067.8937680415</v>
+        <v>447317.6738993236</v>
       </c>
       <c r="R48" t="n">
-        <v>6918659.093284038</v>
+        <v>6918445.963964912</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6029,22 +6018,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110976083</v>
+        <v>110965265</v>
       </c>
       <c r="B49" t="n">
-        <v>96348</v>
+        <v>89369</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6053,45 +6042,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447242.9445623736</v>
+        <v>447265.5391782096</v>
       </c>
       <c r="R49" t="n">
-        <v>6918508.368248228</v>
+        <v>6918615.617490559</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6139,29 +6125,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110963024</v>
+        <v>110966438</v>
       </c>
       <c r="B50" t="n">
-        <v>77267</v>
+        <v>78107</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6174,38 +6159,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447170.915822226</v>
+        <v>447564.2989728634</v>
       </c>
       <c r="R50" t="n">
-        <v>6918653.288937286</v>
+        <v>6918385.033740349</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6259,19 +6244,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>110976092</v>
+        <v>110975542</v>
       </c>
       <c r="B51" t="n">
         <v>77267</v>
@@ -6314,10 +6299,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447184.2951792</v>
+        <v>447292.5455528187</v>
       </c>
       <c r="R51" t="n">
-        <v>6918559.387356906</v>
+        <v>6918619.829575079</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6387,10 +6372,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>110975612</v>
+        <v>110975964</v>
       </c>
       <c r="B52" t="n">
-        <v>89419</v>
+        <v>96348</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6399,30 +6384,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6430,10 +6416,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447588.2014298316</v>
+        <v>447263.7685503919</v>
       </c>
       <c r="R52" t="n">
-        <v>6918398.574047158</v>
+        <v>6918503.401348694</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6503,10 +6489,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110975737</v>
+        <v>110976438</v>
       </c>
       <c r="B53" t="n">
-        <v>77268</v>
+        <v>96348</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6515,30 +6501,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6546,10 +6533,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447306.6016510311</v>
+        <v>447113.0834828347</v>
       </c>
       <c r="R53" t="n">
-        <v>6918450.776842659</v>
+        <v>6918667.653965114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6619,10 +6606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>110975502</v>
+        <v>110962617</v>
       </c>
       <c r="B54" t="n">
-        <v>78081</v>
+        <v>77267</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6635,40 +6622,38 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447233.7729630891</v>
+        <v>447067.8937680415</v>
       </c>
       <c r="R54" t="n">
-        <v>6918662.963441771</v>
+        <v>6918659.093284038</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6716,26 +6701,25 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>110976445</v>
+        <v>110976083</v>
       </c>
       <c r="B55" t="n">
         <v>96348</v>
@@ -6779,10 +6763,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447068.5547254199</v>
+        <v>447242.9445623736</v>
       </c>
       <c r="R55" t="n">
-        <v>6918700.825070715</v>
+        <v>6918508.368248228</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6852,7 +6836,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>110968050</v>
+        <v>110963024</v>
       </c>
       <c r="B56" t="n">
         <v>77267</v>
@@ -6889,17 +6873,17 @@
       <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447317.6738993236</v>
+        <v>447170.915822226</v>
       </c>
       <c r="R56" t="n">
-        <v>6918445.963964912</v>
+        <v>6918653.288937286</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6953,22 +6937,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>110967812</v>
+        <v>110976092</v>
       </c>
       <c r="B57" t="n">
-        <v>77597</v>
+        <v>77267</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6981,38 +6965,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447378.488663816</v>
+        <v>447184.2951792</v>
       </c>
       <c r="R57" t="n">
-        <v>6918384.707011272</v>
+        <v>6918559.387356906</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7060,28 +7046,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>110963160</v>
+        <v>110975612</v>
       </c>
       <c r="B58" t="n">
-        <v>96348</v>
+        <v>89419</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7090,42 +7077,44 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447139.6303205416</v>
+        <v>447588.2014298316</v>
       </c>
       <c r="R58" t="n">
-        <v>6918701.555312089</v>
+        <v>6918398.574047158</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7173,28 +7162,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>110966285</v>
+        <v>110975737</v>
       </c>
       <c r="B59" t="n">
-        <v>88489</v>
+        <v>77268</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7207,38 +7197,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447497.9045277975</v>
+        <v>447306.6016510311</v>
       </c>
       <c r="R59" t="n">
-        <v>6918505.281104221</v>
+        <v>6918450.776842659</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7286,28 +7278,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>110967839</v>
+        <v>110975502</v>
       </c>
       <c r="B60" t="n">
-        <v>88489</v>
+        <v>78081</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7320,38 +7313,40 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447378.488663816</v>
+        <v>447233.7729630891</v>
       </c>
       <c r="R60" t="n">
-        <v>6918384.707011272</v>
+        <v>6918662.963441771</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7399,28 +7394,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>110967352</v>
+        <v>110976445</v>
       </c>
       <c r="B61" t="n">
-        <v>78107</v>
+        <v>96348</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7429,42 +7425,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447457.5581682704</v>
+        <v>447068.5547254199</v>
       </c>
       <c r="R61" t="n">
-        <v>6918361.662466406</v>
+        <v>6918700.825070715</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7512,25 +7511,26 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>110967679</v>
+        <v>110968050</v>
       </c>
       <c r="B62" t="n">
         <v>77267</v>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447428.4321658839</v>
+        <v>447317.6738993236</v>
       </c>
       <c r="R62" t="n">
-        <v>6918370.469648578</v>
+        <v>6918445.963964912</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7643,10 +7643,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>110975574</v>
+        <v>110967812</v>
       </c>
       <c r="B63" t="n">
-        <v>76918</v>
+        <v>77597</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7659,40 +7659,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447267.6561548958</v>
+        <v>447378.488663816</v>
       </c>
       <c r="R63" t="n">
-        <v>6918602.597361922</v>
+        <v>6918384.707011272</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7740,29 +7738,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>110976090</v>
+        <v>110963160</v>
       </c>
       <c r="B64" t="n">
-        <v>78081</v>
+        <v>96348</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7771,44 +7768,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447216.0763635262</v>
+        <v>447139.6303205416</v>
       </c>
       <c r="R64" t="n">
-        <v>6918512.966897782</v>
+        <v>6918701.555312089</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7856,29 +7851,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>110963325</v>
+        <v>110966285</v>
       </c>
       <c r="B65" t="n">
-        <v>96348</v>
+        <v>88489</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7887,39 +7881,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447151.1756012129</v>
+        <v>447497.9045277975</v>
       </c>
       <c r="R65" t="n">
-        <v>6918667.978993148</v>
+        <v>6918505.281104221</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7988,10 +7982,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>110965535</v>
+        <v>110967839</v>
       </c>
       <c r="B66" t="n">
-        <v>76495</v>
+        <v>88489</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8004,38 +7998,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6487</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447365.1558644402</v>
+        <v>447378.488663816</v>
       </c>
       <c r="R66" t="n">
-        <v>6918570.448676185</v>
+        <v>6918384.707011272</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8089,22 +8083,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>110966243</v>
+        <v>110967352</v>
       </c>
       <c r="B67" t="n">
-        <v>76918</v>
+        <v>78107</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8117,35 +8111,35 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447497.9045277975</v>
+        <v>447457.5581682704</v>
       </c>
       <c r="R67" t="n">
-        <v>6918505.281104221</v>
+        <v>6918361.662466406</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8214,10 +8208,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>110966155</v>
+        <v>110967679</v>
       </c>
       <c r="B68" t="n">
-        <v>96348</v>
+        <v>77267</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8226,39 +8220,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447497.9045277975</v>
+        <v>447428.4321658839</v>
       </c>
       <c r="R68" t="n">
-        <v>6918505.281104221</v>
+        <v>6918370.469648578</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8327,10 +8321,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>110966072</v>
+        <v>110975574</v>
       </c>
       <c r="B69" t="n">
-        <v>96348</v>
+        <v>76918</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8339,42 +8333,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447398.736648504</v>
+        <v>447267.6561548958</v>
       </c>
       <c r="R69" t="n">
-        <v>6918579.196305797</v>
+        <v>6918602.597361922</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8416,39 +8412,35 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Matta med 200 plantor</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>110963921</v>
+        <v>110976090</v>
       </c>
       <c r="B70" t="n">
-        <v>89558</v>
+        <v>78081</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8457,42 +8449,44 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447214.3620988361</v>
+        <v>447216.0763635262</v>
       </c>
       <c r="R70" t="n">
-        <v>6918698.518918517</v>
+        <v>6918512.966897782</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8540,25 +8534,26 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>110963587</v>
+        <v>110963325</v>
       </c>
       <c r="B71" t="n">
         <v>96348</v>
@@ -8599,10 +8594,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447158.8766089129</v>
+        <v>447151.1756012129</v>
       </c>
       <c r="R71" t="n">
-        <v>6918685.017929589</v>
+        <v>6918667.978993148</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8671,10 +8666,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>110975632</v>
+        <v>110965535</v>
       </c>
       <c r="B72" t="n">
-        <v>77267</v>
+        <v>76495</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8687,40 +8682,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447635.6922305016</v>
+        <v>447365.1558644402</v>
       </c>
       <c r="R72" t="n">
-        <v>6918346.343155311</v>
+        <v>6918570.448676185</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8768,29 +8761,28 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>110975526</v>
+        <v>110967209</v>
       </c>
       <c r="B73" t="n">
-        <v>76495</v>
+        <v>78081</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8803,40 +8795,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447292.5455528187</v>
+        <v>447471.1999542807</v>
       </c>
       <c r="R73" t="n">
-        <v>6918619.829575079</v>
+        <v>6918254.298169499</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8884,29 +8874,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>110976406</v>
+        <v>110966243</v>
       </c>
       <c r="B74" t="n">
-        <v>89558</v>
+        <v>76918</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8915,44 +8904,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447123.7784161834</v>
+        <v>447497.9045277975</v>
       </c>
       <c r="R74" t="n">
-        <v>6918668.41234626</v>
+        <v>6918505.281104221</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9000,29 +8987,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>110966407</v>
+        <v>110966155</v>
       </c>
       <c r="B75" t="n">
-        <v>77186</v>
+        <v>96348</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9031,42 +9017,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447554.0252953023</v>
+        <v>447497.9045277975</v>
       </c>
       <c r="R75" t="n">
-        <v>6918411.169935671</v>
+        <v>6918505.281104221</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9120,22 +9106,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>110965704</v>
+        <v>110966072</v>
       </c>
       <c r="B76" t="n">
-        <v>77267</v>
+        <v>96348</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9144,25 +9130,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9219,6 +9205,11 @@
       <c r="AB76" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Matta med 200 plantor</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9245,10 +9236,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>110965784</v>
+        <v>110963921</v>
       </c>
       <c r="B77" t="n">
-        <v>76495</v>
+        <v>89558</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9257,25 +9248,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9286,10 +9277,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447398.736648504</v>
+        <v>447214.3620988361</v>
       </c>
       <c r="R77" t="n">
-        <v>6918579.196305797</v>
+        <v>6918698.518918517</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -9358,10 +9349,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>110967175</v>
+        <v>110963587</v>
       </c>
       <c r="B78" t="n">
-        <v>78107</v>
+        <v>96348</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9370,25 +9361,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9399,10 +9390,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447518.4571032667</v>
+        <v>447158.8766089129</v>
       </c>
       <c r="R78" t="n">
-        <v>6918305.50772165</v>
+        <v>6918685.017929589</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9471,10 +9462,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>110965775</v>
+        <v>110975632</v>
       </c>
       <c r="B79" t="n">
-        <v>76918</v>
+        <v>77267</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9487,38 +9478,40 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447398.736648504</v>
+        <v>447635.6922305016</v>
       </c>
       <c r="R79" t="n">
-        <v>6918579.196305797</v>
+        <v>6918346.343155311</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9566,28 +9559,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>110975596</v>
+        <v>110975526</v>
       </c>
       <c r="B80" t="n">
-        <v>77267</v>
+        <v>76495</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9600,21 +9594,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9627,10 +9621,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447490.0481363446</v>
+        <v>447292.5455528187</v>
       </c>
       <c r="R80" t="n">
-        <v>6918419.131989811</v>
+        <v>6918619.829575079</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9700,10 +9694,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>110975925</v>
+        <v>110976406</v>
       </c>
       <c r="B81" t="n">
-        <v>78081</v>
+        <v>89558</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9712,25 +9706,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9743,10 +9737,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447263.7685503919</v>
+        <v>447123.7784161834</v>
       </c>
       <c r="R81" t="n">
-        <v>6918503.401348694</v>
+        <v>6918668.41234626</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9816,7 +9810,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>110962887</v>
+        <v>110966407</v>
       </c>
       <c r="B82" t="n">
         <v>77186</v>
@@ -9857,13 +9851,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447143.1494927733</v>
+        <v>447554.0252953023</v>
       </c>
       <c r="R82" t="n">
-        <v>6918659.757438121</v>
+        <v>6918411.169935671</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9929,10 +9923,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110968274</v>
+        <v>110965704</v>
       </c>
       <c r="B83" t="n">
-        <v>76918</v>
+        <v>77267</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9945,21 +9939,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9970,10 +9964,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447307.8412965431</v>
+        <v>447398.736648504</v>
       </c>
       <c r="R83" t="n">
-        <v>6918441.016784997</v>
+        <v>6918579.196305797</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -10042,10 +10036,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>110964301</v>
+        <v>110965784</v>
       </c>
       <c r="B84" t="n">
-        <v>88489</v>
+        <v>76495</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10058,21 +10052,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10083,10 +10077,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447249.0090083955</v>
+        <v>447398.736648504</v>
       </c>
       <c r="R84" t="n">
-        <v>6918657.157264436</v>
+        <v>6918579.196305797</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -10155,10 +10149,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>110963547</v>
+        <v>110967175</v>
       </c>
       <c r="B85" t="n">
-        <v>90854</v>
+        <v>78107</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10171,38 +10165,38 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447172.0372587139</v>
+        <v>447518.4571032667</v>
       </c>
       <c r="R85" t="n">
-        <v>6918724.232778939</v>
+        <v>6918305.50772165</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10256,22 +10250,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>110968290</v>
+        <v>110965775</v>
       </c>
       <c r="B86" t="n">
-        <v>77268</v>
+        <v>76918</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10284,21 +10278,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10309,10 +10303,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447307.8412965431</v>
+        <v>447398.736648504</v>
       </c>
       <c r="R86" t="n">
-        <v>6918441.016784997</v>
+        <v>6918579.196305797</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -10381,10 +10375,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>110966477</v>
+        <v>110967074</v>
       </c>
       <c r="B87" t="n">
-        <v>78107</v>
+        <v>96348</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10393,39 +10387,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447573.2389177232</v>
+        <v>447571.4109653771</v>
       </c>
       <c r="R87" t="n">
-        <v>6918392.314952057</v>
+        <v>6918216.543616171</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -10494,10 +10488,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>110975610</v>
+        <v>110975596</v>
       </c>
       <c r="B88" t="n">
-        <v>78107</v>
+        <v>77267</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10510,21 +10504,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10537,10 +10531,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447588.2014298316</v>
+        <v>447490.0481363446</v>
       </c>
       <c r="R88" t="n">
-        <v>6918398.574047158</v>
+        <v>6918419.131989811</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10610,10 +10604,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>110975709</v>
+        <v>110975925</v>
       </c>
       <c r="B89" t="n">
-        <v>77268</v>
+        <v>78081</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10626,21 +10620,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10653,10 +10647,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447556.0960817932</v>
+        <v>447263.7685503919</v>
       </c>
       <c r="R89" t="n">
-        <v>6918306.308510381</v>
+        <v>6918503.401348694</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10726,10 +10720,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>110964240</v>
+        <v>110962887</v>
       </c>
       <c r="B90" t="n">
-        <v>89419</v>
+        <v>77186</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10742,38 +10736,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447232.2188176445</v>
+        <v>447143.1494927733</v>
       </c>
       <c r="R90" t="n">
-        <v>6918652.784268363</v>
+        <v>6918659.757438121</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10827,22 +10821,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>110975567</v>
+        <v>110968274</v>
       </c>
       <c r="B91" t="n">
-        <v>77268</v>
+        <v>76918</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10855,40 +10849,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447280.384271103</v>
+        <v>447307.8412965431</v>
       </c>
       <c r="R91" t="n">
-        <v>6918614.455664258</v>
+        <v>6918441.016784997</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10936,29 +10928,28 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>110975637</v>
+        <v>110964301</v>
       </c>
       <c r="B92" t="n">
-        <v>76918</v>
+        <v>88489</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10971,40 +10962,38 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447621.9338528389</v>
+        <v>447249.0090083955</v>
       </c>
       <c r="R92" t="n">
-        <v>6918328.00482947</v>
+        <v>6918657.157264436</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11052,29 +11041,28 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>110975731</v>
+        <v>110963547</v>
       </c>
       <c r="B93" t="n">
-        <v>76918</v>
+        <v>90854</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11087,40 +11075,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447316.6647167787</v>
+        <v>447172.0372587139</v>
       </c>
       <c r="R93" t="n">
-        <v>6918440.877694603</v>
+        <v>6918724.232778939</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11168,29 +11154,28 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>110967950</v>
+        <v>110968290</v>
       </c>
       <c r="B94" t="n">
-        <v>89558</v>
+        <v>77268</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11199,25 +11184,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11228,10 +11213,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447335.9280005182</v>
+        <v>447307.8412965431</v>
       </c>
       <c r="R94" t="n">
-        <v>6918425.267536594</v>
+        <v>6918441.016784997</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -11300,10 +11285,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>110967596</v>
+        <v>110966477</v>
       </c>
       <c r="B95" t="n">
-        <v>77267</v>
+        <v>78107</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11316,35 +11301,35 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447491.3447608051</v>
+        <v>447573.2389177232</v>
       </c>
       <c r="R95" t="n">
-        <v>6918383.39599544</v>
+        <v>6918392.314952057</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -11413,10 +11398,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>110967665</v>
+        <v>110975610</v>
       </c>
       <c r="B96" t="n">
-        <v>77268</v>
+        <v>78107</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11429,38 +11414,40 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447438.3814675056</v>
+        <v>447588.2014298316</v>
       </c>
       <c r="R96" t="n">
-        <v>6918382.836934499</v>
+        <v>6918398.574047158</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11508,28 +11495,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>110975587</v>
+        <v>110975709</v>
       </c>
       <c r="B97" t="n">
-        <v>76918</v>
+        <v>77268</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11542,21 +11530,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11569,10 +11557,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447506.0012030424</v>
+        <v>447556.0960817932</v>
       </c>
       <c r="R97" t="n">
-        <v>6918488.456190935</v>
+        <v>6918306.308510381</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11642,10 +11630,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>110975625</v>
+        <v>110964240</v>
       </c>
       <c r="B98" t="n">
-        <v>78081</v>
+        <v>89419</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11658,40 +11646,38 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447635.8447960903</v>
+        <v>447232.2188176445</v>
       </c>
       <c r="R98" t="n">
-        <v>6918356.081520229</v>
+        <v>6918652.784268363</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11739,29 +11725,28 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>110975509</v>
+        <v>110975567</v>
       </c>
       <c r="B99" t="n">
-        <v>76495</v>
+        <v>77268</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11774,21 +11759,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11801,10 +11786,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447235.1367591074</v>
+        <v>447280.384271103</v>
       </c>
       <c r="R99" t="n">
-        <v>6918661.086691698</v>
+        <v>6918614.455664258</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11874,7 +11859,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>110975590</v>
+        <v>110975637</v>
       </c>
       <c r="B100" t="n">
         <v>76918</v>
@@ -11917,10 +11902,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447490.0481363446</v>
+        <v>447621.9338528389</v>
       </c>
       <c r="R100" t="n">
-        <v>6918419.131989811</v>
+        <v>6918328.00482947</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11990,10 +11975,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>110966259</v>
+        <v>110975731</v>
       </c>
       <c r="B101" t="n">
-        <v>77515</v>
+        <v>76918</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12006,38 +11991,40 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vålkojan S Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447497.9045277975</v>
+        <v>447316.6647167787</v>
       </c>
       <c r="R101" t="n">
-        <v>6918505.281104221</v>
+        <v>6918440.877694603</v>
       </c>
       <c r="S101" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12085,28 +12072,29 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>110975497</v>
+        <v>110967950</v>
       </c>
       <c r="B102" t="n">
-        <v>76918</v>
+        <v>89558</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12115,44 +12103,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447233.7729630891</v>
+        <v>447335.9280005182</v>
       </c>
       <c r="R102" t="n">
-        <v>6918662.963441771</v>
+        <v>6918425.267536594</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12200,29 +12186,28 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Kämpedal</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>110964185</v>
+        <v>110967596</v>
       </c>
       <c r="B103" t="n">
-        <v>76918</v>
+        <v>77267</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12235,21 +12220,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12260,10 +12245,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447238.1017849073</v>
+        <v>447491.3447608051</v>
       </c>
       <c r="R103" t="n">
-        <v>6918642.951452344</v>
+        <v>6918383.39599544</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -12332,10 +12317,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>110965171</v>
+        <v>110967665</v>
       </c>
       <c r="B104" t="n">
-        <v>88489</v>
+        <v>77268</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12348,21 +12333,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12373,10 +12358,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447265.5391782096</v>
+        <v>447438.3814675056</v>
       </c>
       <c r="R104" t="n">
-        <v>6918615.617490559</v>
+        <v>6918382.836934499</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -12445,10 +12430,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>110965307</v>
+        <v>110975587</v>
       </c>
       <c r="B105" t="n">
-        <v>77267</v>
+        <v>76918</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12461,38 +12446,40 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vålkojan O, Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447291.9897770986</v>
+        <v>447506.0012030424</v>
       </c>
       <c r="R105" t="n">
-        <v>6918584.588592289</v>
+        <v>6918488.456190935</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12540,28 +12527,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>110975619</v>
+        <v>110975625</v>
       </c>
       <c r="B106" t="n">
-        <v>76495</v>
+        <v>78081</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12574,21 +12562,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12674,7 +12662,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>110976022</v>
+        <v>110975509</v>
       </c>
       <c r="B107" t="n">
         <v>76495</v>
@@ -12717,10 +12705,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447263.7685503919</v>
+        <v>447235.1367591074</v>
       </c>
       <c r="R107" t="n">
-        <v>6918503.401348694</v>
+        <v>6918661.086691698</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12790,10 +12778,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>110975722</v>
+        <v>110975590</v>
       </c>
       <c r="B108" t="n">
-        <v>77267</v>
+        <v>76918</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12806,21 +12794,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12833,10 +12821,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447398.6229754346</v>
+        <v>447490.0481363446</v>
       </c>
       <c r="R108" t="n">
-        <v>6918365.372506417</v>
+        <v>6918419.131989811</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12906,10 +12894,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>110965547</v>
+        <v>110966259</v>
       </c>
       <c r="B109" t="n">
-        <v>76918</v>
+        <v>77515</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12922,38 +12910,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan S Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447365.1558644402</v>
+        <v>447497.9045277975</v>
       </c>
       <c r="R109" t="n">
-        <v>6918570.448676185</v>
+        <v>6918505.281104221</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13007,22 +12995,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>110962609</v>
+        <v>110975497</v>
       </c>
       <c r="B110" t="n">
-        <v>76930</v>
+        <v>76918</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13035,38 +13023,40 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>502</v>
+        <v>6437</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ladlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Calicium tigillare</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Pers.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447067.8937680415</v>
+        <v>447233.7729630891</v>
       </c>
       <c r="R110" t="n">
-        <v>6918659.093284038</v>
+        <v>6918662.963441771</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13114,28 +13104,29 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Kämpedal</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>115247194</v>
+        <v>110964185</v>
       </c>
       <c r="B111" t="n">
-        <v>79074</v>
+        <v>76918</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13148,37 +13139,38 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Vålkojan O, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447554</v>
+        <v>447238.1017849073</v>
       </c>
       <c r="R111" t="n">
-        <v>6918411</v>
+        <v>6918642.951452344</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13202,12 +13194,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13222,15 +13224,917 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110965171</v>
+      </c>
+      <c r="B112" t="n">
+        <v>88489</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Vålkojan O, Hjd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>447265.5391782096</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6918615.617490559</v>
+      </c>
+      <c r="S112" t="n">
+        <v>20</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>110965307</v>
+      </c>
+      <c r="B113" t="n">
+        <v>77267</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Vålkojan O, Hjd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>447291.9897770986</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6918584.588592289</v>
+      </c>
+      <c r="S113" t="n">
+        <v>20</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>110975619</v>
+      </c>
+      <c r="B114" t="n">
+        <v>76495</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>447635.8447960903</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6918356.081520229</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Martin Kämpedal</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Martin Kämpedal</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>110976022</v>
+      </c>
+      <c r="B115" t="n">
+        <v>76495</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>447263.7685503919</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6918503.401348694</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Martin Kämpedal</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Martin Kämpedal</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>110975722</v>
+      </c>
+      <c r="B116" t="n">
+        <v>77267</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>447398.6229754346</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6918365.372506417</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Martin Kämpedal</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Martin Kämpedal</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>110965547</v>
+      </c>
+      <c r="B117" t="n">
+        <v>76918</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>447365.1558644402</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6918570.448676185</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
           <t>Bjarne Tutturen</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
+      <c r="AX117" t="inlineStr">
         <is>
           <t>Bjarne Tutturen</t>
         </is>
       </c>
-      <c r="AY111" t="inlineStr"/>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>110962609</v>
+      </c>
+      <c r="B118" t="n">
+        <v>76930</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>502</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ladlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Calicium tigillare</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Pers.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>447067.8937680415</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6918659.093284038</v>
+      </c>
+      <c r="S118" t="n">
+        <v>25</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>115247194</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79074</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>447554</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6918411</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42342-2022 artfynd.xlsx
+++ b/artfynd/A 42342-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY128"/>
+  <dimension ref="A1:AZ128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110962887</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966407</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110968694</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110962609</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115247963</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285005</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1566,6 +1611,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967812</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,6 +1714,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226503</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966770</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975647</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110964240</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110964390</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2160,6 +2235,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975612</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963921</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965155</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2454,6 +2544,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965631</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2552,6 +2647,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967950</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2653,6 +2753,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975517</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2754,6 +2859,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975579</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2855,6 +2965,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976406</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2953,6 +3068,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110964301</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3051,6 +3171,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965171</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3149,6 +3274,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966285</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3247,6 +3377,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967839</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3345,6 +3480,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963547</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3443,6 +3583,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965265</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3541,6 +3686,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966259</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3639,6 +3789,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110964185</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3737,6 +3892,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965547</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3835,6 +3995,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965775</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3933,6 +4098,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966243</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4031,6 +4201,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966444</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4129,6 +4304,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110968274</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4230,6 +4410,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975497</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4331,6 +4516,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975574</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4432,6 +4622,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975587</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4533,6 +4728,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975590</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4634,6 +4834,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975637</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4735,6 +4940,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975731</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4836,6 +5046,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975795</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4944,6 +5159,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797097</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5042,6 +5262,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110962617</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5140,6 +5365,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963024</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5238,6 +5468,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965307</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5336,6 +5571,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965704</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5434,6 +5674,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967596</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5532,6 +5777,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967679</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5630,6 +5880,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110968050</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5731,6 +5986,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975542</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5832,6 +6092,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975558</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5933,6 +6198,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975596</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6034,6 +6304,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975632</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6135,6 +6410,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975722</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6236,6 +6516,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976092</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6344,6 +6629,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797111</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6452,6 +6742,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797119</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6550,6 +6845,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965310</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6648,6 +6948,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966278</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6746,6 +7051,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966438</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6844,6 +7154,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966477</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6942,6 +7257,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966966</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7040,6 +7360,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967175</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7138,6 +7463,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967352</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7239,6 +7569,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975610</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7347,6 +7682,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797047</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7455,6 +7795,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797050</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7563,6 +7908,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797069</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7671,6 +8021,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797077</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7779,6 +8134,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104797087</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7880,6 +8240,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975486</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7981,6 +8346,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976451</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8078,6 +8448,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115248063</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8179,6 +8554,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284997</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8277,6 +8657,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226538</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8375,6 +8760,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965535</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8473,6 +8863,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965784</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8571,6 +8966,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966545</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8669,6 +9069,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110968265</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8770,6 +9175,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975509</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8871,6 +9281,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975526</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8972,6 +9387,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975584</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9073,6 +9493,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975619</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9174,6 +9599,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976022</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9275,6 +9705,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976079</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9373,6 +9808,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110962547</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9471,6 +9911,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963160</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9569,6 +10014,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963196</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9667,6 +10117,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963325</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9765,6 +10220,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963587</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9863,6 +10323,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110963829</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9961,6 +10426,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965319</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10064,6 +10534,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966072</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10162,6 +10637,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966155</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10260,6 +10740,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967074</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10358,6 +10843,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969075</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10460,6 +10950,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975458</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10562,6 +11057,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975964</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10664,6 +11164,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976083</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10766,6 +11271,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976192</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10868,6 +11378,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976438</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10970,6 +11485,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976445</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11088,6 +11608,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293639</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11186,6 +11711,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110962666</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11284,6 +11814,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967665</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11382,6 +11917,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110968290</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11483,6 +12023,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975567</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11584,6 +12129,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975709</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11685,6 +12235,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975737</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11786,6 +12341,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284995</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11883,6 +12443,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115248009</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11981,6 +12546,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110962616</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12079,6 +12649,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110962674</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12177,6 +12752,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965542</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12275,6 +12855,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110965691</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12373,6 +12958,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966289</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12471,6 +13061,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110966541</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12569,6 +13164,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110967209</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12670,6 +13270,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975502</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12771,6 +13376,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975625</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12872,6 +13482,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975705</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12973,6 +13588,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975716</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13074,6 +13694,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110975925</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13175,6 +13800,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976090</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13276,6 +13906,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110976097</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13373,8 +14008,142 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115247194</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>